--- a/format_excel/Ware_Gen_clean.xlsx
+++ b/format_excel/Ware_Gen_clean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://atvtireinc-my.sharepoint.com/personal/vjdelrosario_avatco_com/Documents/Desktop/MWF Offers/format_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="468" documentId="11_F25DC773A252ABDACC1048891919571A5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63916A6F-49BB-4037-A9CE-3156C24237B3}"/>
+  <xr:revisionPtr revIDLastSave="493" documentId="11_F25DC773A252ABDACC1048891919571A5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77BB443A-A7F8-43EC-8287-3D11FA1B4E19}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="9270" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -182,15 +182,6 @@
     <t>Apopka TOTAL AMOUNT LOAD:</t>
   </si>
   <si>
-    <t>Winchester TOTAL AMOUNT LOAD:</t>
-  </si>
-  <si>
-    <t>Winchester Total Weight (full load met at 42k lbs):</t>
-  </si>
-  <si>
-    <t>Winchester Total Piece Count:</t>
-  </si>
-  <si>
     <t>Miami TOTAL AMOUNT LOAD:</t>
   </si>
   <si>
@@ -207,10 +198,6 @@
   </si>
   <si>
     <t>Bloomsburg Total Piece Count:</t>
-  </si>
-  <si>
-    <t>Winchester On
-Hand Inventory</t>
   </si>
   <si>
     <t>Miami On
@@ -221,16 +208,29 @@
 Hand Inventory</t>
   </si>
   <si>
-    <t>Tenesse TOTAL AMOUNT LOAD:</t>
-  </si>
-  <si>
-    <t>Tennesse Total Weight (full load met at 42k lbs):</t>
-  </si>
-  <si>
-    <t>Tennesse Total Piece Count:</t>
-  </si>
-  <si>
-    <t>Tennesse On
+    <t>Winchester, Tenesse TOTAL AMOUNT LOAD:</t>
+  </si>
+  <si>
+    <t>Winchester, Tennesse Total Weight (full load met at 42k lbs):</t>
+  </si>
+  <si>
+    <t>Winchester, Tennesse Total Piece Count:</t>
+  </si>
+  <si>
+    <t>Winchester, Tennesse On
+Hand Inventory</t>
+  </si>
+  <si>
+    <t>Winchester, Kentucky TOTAL AMOUNT LOAD:</t>
+  </si>
+  <si>
+    <t>Winchester, Kentucky Total Weight (full load met at 42k lbs):</t>
+  </si>
+  <si>
+    <t>Winchester, Kentucky Total Piece Count:</t>
+  </si>
+  <si>
+    <t>Winchester, Kentucky On
 Hand Inventory</t>
   </si>
 </sst>
@@ -378,41 +378,41 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -716,17 +716,15 @@
     <col min="10" max="10" width="13.140625" style="1" customWidth="1"/>
     <col min="11" max="11" width="13.7109375" customWidth="1"/>
     <col min="12" max="12" width="9.140625" style="1" customWidth="1"/>
-    <col min="13" max="15" width="9.140625" customWidth="1"/>
-    <col min="16" max="16" width="19.7109375" customWidth="1"/>
+    <col min="13" max="14" width="9.140625" customWidth="1"/>
+    <col min="15" max="16" width="3.7109375" customWidth="1"/>
     <col min="17" max="17" width="32.140625" customWidth="1"/>
     <col min="18" max="18" width="15.85546875" style="1" customWidth="1"/>
     <col min="19" max="19" width="15.5703125" customWidth="1"/>
     <col min="20" max="20" width="16" style="1" customWidth="1"/>
     <col min="21" max="21" width="9.140625" customWidth="1"/>
     <col min="22" max="22" width="14.140625" customWidth="1"/>
-    <col min="23" max="23" width="9.140625" customWidth="1"/>
-    <col min="24" max="24" width="9.28515625" customWidth="1"/>
-    <col min="25" max="25" width="9.140625" customWidth="1"/>
+    <col min="23" max="25" width="3.7109375" customWidth="1"/>
     <col min="26" max="26" width="20.7109375" customWidth="1"/>
     <col min="27" max="27" width="17.5703125" customWidth="1"/>
     <col min="28" max="28" width="19.42578125" customWidth="1"/>
@@ -736,16 +734,14 @@
     <col min="32" max="32" width="19.7109375" style="1" customWidth="1"/>
     <col min="33" max="33" width="9.140625" customWidth="1"/>
     <col min="34" max="34" width="16.140625" customWidth="1"/>
-    <col min="35" max="37" width="9.140625" customWidth="1"/>
+    <col min="35" max="37" width="3.7109375" customWidth="1"/>
     <col min="38" max="38" width="14" customWidth="1"/>
     <col min="39" max="39" width="32" style="1" customWidth="1"/>
     <col min="40" max="40" width="16" customWidth="1"/>
     <col min="41" max="41" width="12.5703125" style="1" customWidth="1"/>
     <col min="42" max="42" width="8.7109375" customWidth="1"/>
     <col min="43" max="43" width="16.42578125" customWidth="1"/>
-    <col min="44" max="44" width="9.140625" customWidth="1"/>
-    <col min="45" max="45" width="7.42578125" customWidth="1"/>
-    <col min="46" max="46" width="9.140625" customWidth="1"/>
+    <col min="44" max="46" width="3.7109375" customWidth="1"/>
     <col min="47" max="47" width="13.140625" customWidth="1"/>
     <col min="48" max="48" width="14.140625" style="1" customWidth="1"/>
     <col min="49" max="49" width="21.140625" customWidth="1"/>
@@ -753,84 +749,93 @@
     <col min="51" max="51" width="11.85546875" customWidth="1"/>
     <col min="52" max="52" width="18.28515625" customWidth="1"/>
     <col min="53" max="53" width="13.28515625" customWidth="1"/>
-    <col min="54" max="55" width="9.140625" customWidth="1"/>
+    <col min="54" max="55" width="3.7109375" customWidth="1"/>
     <col min="56" max="56" width="18.28515625" customWidth="1"/>
     <col min="57" max="57" width="18" customWidth="1"/>
     <col min="58" max="58" width="18.5703125" customWidth="1"/>
     <col min="59" max="59" width="17.42578125" customWidth="1"/>
-    <col min="60" max="64" width="9.140625" customWidth="1"/>
+    <col min="60" max="62" width="9.140625" customWidth="1"/>
+    <col min="63" max="64" width="3.7109375" customWidth="1"/>
     <col min="65" max="65" width="18.28515625" customWidth="1"/>
     <col min="66" max="66" width="18" customWidth="1"/>
     <col min="67" max="67" width="18.5703125" customWidth="1"/>
     <col min="68" max="68" width="17.42578125" customWidth="1"/>
-    <col min="69" max="73" width="9.140625" customWidth="1"/>
+    <col min="69" max="71" width="9.140625" customWidth="1"/>
+    <col min="72" max="73" width="3.7109375" customWidth="1"/>
     <col min="74" max="74" width="18.28515625" customWidth="1"/>
     <col min="75" max="75" width="18" customWidth="1"/>
     <col min="76" max="76" width="18.5703125" customWidth="1"/>
     <col min="77" max="77" width="17.42578125" customWidth="1"/>
-    <col min="78" max="82" width="9.140625" customWidth="1"/>
+    <col min="78" max="80" width="9.140625" customWidth="1"/>
+    <col min="81" max="82" width="3.7109375" customWidth="1"/>
     <col min="83" max="83" width="18.28515625" customWidth="1"/>
     <col min="84" max="84" width="18" customWidth="1"/>
     <col min="85" max="85" width="18.5703125" customWidth="1"/>
     <col min="86" max="86" width="17.42578125" customWidth="1"/>
-    <col min="87" max="120" width="9.140625" customWidth="1"/>
+    <col min="87" max="89" width="9.140625" customWidth="1"/>
+    <col min="90" max="91" width="3.7109375" customWidth="1"/>
+    <col min="92" max="92" width="17.140625" customWidth="1"/>
+    <col min="93" max="93" width="14.140625" customWidth="1"/>
+    <col min="94" max="94" width="14" customWidth="1"/>
+    <col min="95" max="95" width="11" customWidth="1"/>
+    <col min="96" max="120" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:98" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="25" t="s">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="28" t="s">
+      <c r="C1" s="21"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="28"/>
-      <c r="G1" s="27">
+      <c r="F1" s="27"/>
+      <c r="G1" s="26">
         <f>SUM(L6:L3000)</f>
         <v>0</v>
       </c>
-      <c r="H1" s="27"/>
+      <c r="H1" s="26"/>
       <c r="I1" s="6"/>
       <c r="J1" s="7"/>
       <c r="K1" s="8"/>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
       <c r="P1" s="9"/>
       <c r="Q1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="22">
+      <c r="R1" s="18">
         <f>SUM(T6:T3000)</f>
         <v>0</v>
       </c>
-      <c r="S1" s="22"/>
+      <c r="S1" s="18"/>
       <c r="T1" s="11"/>
       <c r="U1" s="11"/>
       <c r="V1" s="5"/>
       <c r="W1" s="5"/>
       <c r="X1" s="5"/>
       <c r="Y1" s="9"/>
-      <c r="Z1" s="21" t="s">
+      <c r="Z1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="AA1" s="21"/>
+      <c r="AA1" s="23"/>
       <c r="AB1" s="9"/>
-      <c r="AC1" s="29" t="s">
+      <c r="AC1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="29"/>
-      <c r="AE1" s="22">
+      <c r="AD1" s="19"/>
+      <c r="AE1" s="18">
         <f>SUM(AF6:AF3000)</f>
         <v>0</v>
       </c>
-      <c r="AF1" s="22"/>
-      <c r="AG1" s="22"/>
+      <c r="AF1" s="18"/>
+      <c r="AG1" s="18"/>
       <c r="AH1" s="5"/>
       <c r="AI1" s="5"/>
       <c r="AJ1" s="5"/>
@@ -839,12 +844,12 @@
         <v>6</v>
       </c>
       <c r="AM1" s="17"/>
-      <c r="AN1" s="22">
+      <c r="AN1" s="18">
         <f>SUM(AO6:AO3000)</f>
         <v>0</v>
       </c>
-      <c r="AO1" s="22"/>
-      <c r="AP1" s="22"/>
+      <c r="AO1" s="18"/>
+      <c r="AP1" s="18"/>
       <c r="AQ1" s="11"/>
       <c r="AR1" s="5"/>
       <c r="AS1" s="5"/>
@@ -854,90 +859,90 @@
       </c>
       <c r="AV1" s="17"/>
       <c r="AW1" s="17"/>
-      <c r="AX1" s="22">
+      <c r="AX1" s="18">
         <f>SUM(AX6:AX3000)</f>
         <v>0</v>
       </c>
-      <c r="AY1" s="22"/>
-      <c r="AZ1" s="22"/>
+      <c r="AY1" s="18"/>
+      <c r="AZ1" s="18"/>
       <c r="BA1" s="5"/>
       <c r="BD1" s="17" t="s">
         <v>45</v>
       </c>
       <c r="BE1" s="17"/>
       <c r="BF1" s="17"/>
-      <c r="BG1" s="22">
+      <c r="BG1" s="18">
         <f>SUM(BG6:BG3000)</f>
         <v>0</v>
       </c>
-      <c r="BH1" s="22"/>
-      <c r="BI1" s="22"/>
+      <c r="BH1" s="18"/>
+      <c r="BI1" s="18"/>
       <c r="BJ1" s="5"/>
       <c r="BM1" s="17" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="BN1" s="17"/>
       <c r="BO1" s="17"/>
-      <c r="BP1" s="22">
+      <c r="BP1" s="18">
         <f>SUM(BP6:BP3000)</f>
         <v>0</v>
       </c>
-      <c r="BQ1" s="22"/>
-      <c r="BR1" s="22"/>
+      <c r="BQ1" s="18"/>
+      <c r="BR1" s="18"/>
       <c r="BS1" s="5"/>
       <c r="BV1" s="17" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="BW1" s="17"/>
       <c r="BX1" s="17"/>
-      <c r="BY1" s="22">
+      <c r="BY1" s="18">
         <f>SUM(BY6:BY3000)</f>
         <v>0</v>
       </c>
-      <c r="BZ1" s="22"/>
-      <c r="CA1" s="22"/>
+      <c r="BZ1" s="18"/>
+      <c r="CA1" s="18"/>
       <c r="CB1" s="5"/>
       <c r="CE1" s="17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="CF1" s="17"/>
       <c r="CG1" s="17"/>
-      <c r="CH1" s="22">
+      <c r="CH1" s="18">
         <f>SUM(CH6:CH3000)</f>
         <v>0</v>
       </c>
-      <c r="CI1" s="22"/>
-      <c r="CJ1" s="22"/>
+      <c r="CI1" s="18"/>
+      <c r="CJ1" s="18"/>
       <c r="CK1" s="5"/>
       <c r="CN1" s="17" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="CO1" s="17"/>
       <c r="CP1" s="17"/>
-      <c r="CQ1" s="22">
+      <c r="CQ1" s="18">
         <f>SUM(CQ6:CQ3000)</f>
         <v>0</v>
       </c>
-      <c r="CR1" s="22"/>
-      <c r="CS1" s="22"/>
+      <c r="CR1" s="18"/>
+      <c r="CS1" s="18"/>
       <c r="CT1" s="5"/>
     </row>
     <row r="2" spans="1:98" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24"/>
+      <c r="A2" s="20"/>
       <c r="B2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="19" t="s">
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19">
+      <c r="F2" s="25"/>
+      <c r="G2" s="25">
         <f>SUM(O6:O3000)</f>
         <v>0</v>
       </c>
-      <c r="H2" s="19"/>
+      <c r="H2" s="25"/>
       <c r="I2" s="3" t="str">
         <f>IF(G2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
@@ -1036,7 +1041,7 @@
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
       <c r="BM2" s="17" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="BN2" s="17"/>
       <c r="BO2" s="17"/>
@@ -1051,7 +1056,7 @@
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
       <c r="BV2" s="17" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="BW2" s="17"/>
       <c r="BX2" s="17"/>
@@ -1066,7 +1071,7 @@
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
       <c r="CE2" s="17" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="CF2" s="17"/>
       <c r="CG2" s="17"/>
@@ -1081,7 +1086,7 @@
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
       <c r="CN2" s="17" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="CO2" s="17"/>
       <c r="CP2" s="17"/>
@@ -1097,23 +1102,23 @@
       </c>
     </row>
     <row r="3" spans="1:98" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24"/>
+      <c r="A3" s="20"/>
       <c r="B3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="19" t="s">
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="18">
+      <c r="F3" s="25"/>
+      <c r="G3" s="28">
         <f>SUM(K6:K3000)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
       <c r="K3" s="3"/>
       <c r="L3" s="5"/>
       <c r="M3" s="5"/>
@@ -1123,13 +1128,13 @@
       <c r="Q3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="18">
+      <c r="R3" s="28">
         <f>SUM(S6:S3000)</f>
         <v>0</v>
       </c>
-      <c r="S3" s="18"/>
-      <c r="T3" s="18"/>
-      <c r="U3" s="18"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
       <c r="V3" s="3"/>
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
@@ -1192,7 +1197,7 @@
       <c r="BI3" s="17"/>
       <c r="BJ3" s="5"/>
       <c r="BM3" s="17" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BN3" s="17"/>
       <c r="BO3" s="17"/>
@@ -1204,7 +1209,7 @@
       <c r="BR3" s="17"/>
       <c r="BS3" s="5"/>
       <c r="BV3" s="17" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="BW3" s="17"/>
       <c r="BX3" s="17"/>
@@ -1216,7 +1221,7 @@
       <c r="CA3" s="17"/>
       <c r="CB3" s="5"/>
       <c r="CE3" s="17" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="CF3" s="17"/>
       <c r="CG3" s="17"/>
@@ -1228,7 +1233,7 @@
       <c r="CJ3" s="17"/>
       <c r="CK3" s="5"/>
       <c r="CN3" s="17" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="CO3" s="17"/>
       <c r="CP3" s="17"/>
@@ -1245,16 +1250,16 @@
       <c r="B4" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="19" t="s">
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
@@ -1336,7 +1341,7 @@
       <c r="CS4" s="12"/>
       <c r="CT4" s="5"/>
     </row>
-    <row r="5" spans="1:98" s="2" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:98" s="2" customFormat="1" ht="63" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>22</v>
       </c>
@@ -1492,7 +1497,7 @@
       </c>
       <c r="BJ5" s="5"/>
       <c r="BM5" s="4" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="BN5" s="4" t="s">
         <v>31</v>
@@ -1511,7 +1516,7 @@
       </c>
       <c r="BS5" s="5"/>
       <c r="BV5" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="BW5" s="4" t="s">
         <v>31</v>
@@ -1530,7 +1535,7 @@
       </c>
       <c r="CB5" s="5"/>
       <c r="CE5" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="CF5" s="4" t="s">
         <v>31</v>
@@ -1549,7 +1554,7 @@
       </c>
       <c r="CK5" s="5"/>
       <c r="CN5" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="CO5" s="4" t="s">
         <v>31</v>
@@ -1570,20 +1575,55 @@
     </row>
   </sheetData>
   <mergeCells count="77">
-    <mergeCell ref="CN4:CQ4"/>
-    <mergeCell ref="CN1:CP1"/>
-    <mergeCell ref="CQ1:CS1"/>
-    <mergeCell ref="CN2:CP2"/>
-    <mergeCell ref="CQ2:CS2"/>
-    <mergeCell ref="CN3:CP3"/>
-    <mergeCell ref="CQ3:CS3"/>
-    <mergeCell ref="CE4:CH4"/>
-    <mergeCell ref="CE1:CG1"/>
-    <mergeCell ref="CH1:CJ1"/>
-    <mergeCell ref="CE2:CG2"/>
-    <mergeCell ref="CH2:CJ2"/>
-    <mergeCell ref="CE3:CG3"/>
-    <mergeCell ref="CH3:CJ3"/>
+    <mergeCell ref="AC4:AF4"/>
+    <mergeCell ref="AL4:AO4"/>
+    <mergeCell ref="AU4:AX4"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="AE3:AG3"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AL2:AM2"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="AN2:AP2"/>
+    <mergeCell ref="AN3:AP3"/>
+    <mergeCell ref="AN1:AP1"/>
+    <mergeCell ref="BD4:BG4"/>
+    <mergeCell ref="AX1:AZ1"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AU3:AW3"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="AX3:AZ3"/>
+    <mergeCell ref="AU1:AW1"/>
+    <mergeCell ref="BD1:BF1"/>
+    <mergeCell ref="BG1:BI1"/>
+    <mergeCell ref="BD2:BF2"/>
+    <mergeCell ref="BG2:BI2"/>
+    <mergeCell ref="BD3:BF3"/>
+    <mergeCell ref="BG3:BI3"/>
     <mergeCell ref="BM4:BP4"/>
     <mergeCell ref="BV1:BX1"/>
     <mergeCell ref="BY1:CA1"/>
@@ -1598,55 +1638,20 @@
     <mergeCell ref="BP2:BR2"/>
     <mergeCell ref="BM3:BO3"/>
     <mergeCell ref="BP3:BR3"/>
-    <mergeCell ref="BD4:BG4"/>
-    <mergeCell ref="AX1:AZ1"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AU3:AW3"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="AX3:AZ3"/>
-    <mergeCell ref="AU1:AW1"/>
-    <mergeCell ref="BD1:BF1"/>
-    <mergeCell ref="BG1:BI1"/>
-    <mergeCell ref="BD2:BF2"/>
-    <mergeCell ref="BG2:BI2"/>
-    <mergeCell ref="BD3:BF3"/>
-    <mergeCell ref="BG3:BI3"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AL2:AM2"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="AN2:AP2"/>
-    <mergeCell ref="AN3:AP3"/>
-    <mergeCell ref="AN1:AP1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE2:AG2"/>
-    <mergeCell ref="AE3:AG3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="Q4:T4"/>
-    <mergeCell ref="AC4:AF4"/>
-    <mergeCell ref="AL4:AO4"/>
-    <mergeCell ref="AU4:AX4"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="CE4:CH4"/>
+    <mergeCell ref="CE1:CG1"/>
+    <mergeCell ref="CH1:CJ1"/>
+    <mergeCell ref="CE2:CG2"/>
+    <mergeCell ref="CH2:CJ2"/>
+    <mergeCell ref="CE3:CG3"/>
+    <mergeCell ref="CH3:CJ3"/>
+    <mergeCell ref="CN4:CQ4"/>
+    <mergeCell ref="CN1:CP1"/>
+    <mergeCell ref="CQ1:CS1"/>
+    <mergeCell ref="CN2:CP2"/>
+    <mergeCell ref="CQ2:CS2"/>
+    <mergeCell ref="CN3:CP3"/>
+    <mergeCell ref="CQ3:CS3"/>
   </mergeCells>
   <conditionalFormatting sqref="G2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">

--- a/format_excel/Ware_Gen_clean.xlsx
+++ b/format_excel/Ware_Gen_clean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://atvtireinc-my.sharepoint.com/personal/vjdelrosario_avatco_com/Documents/Desktop/MWF Offers/format_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="493" documentId="11_F25DC773A252ABDACC1048891919571A5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77BB443A-A7F8-43EC-8287-3D11FA1B4E19}"/>
+  <xr:revisionPtr revIDLastSave="511" documentId="11_F25DC773A252ABDACC1048891919571A5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{648991D6-EAA3-42BB-8FB9-2AD4213881F6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -300,7 +300,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -323,11 +323,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -345,12 +358,6 @@
     <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -366,9 +373,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -378,47 +382,57 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -782,563 +796,563 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:98" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="27" t="s">
+      <c r="C1" s="22"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="27"/>
-      <c r="G1" s="26">
+      <c r="K1" s="25"/>
+      <c r="L1" s="19">
         <f>SUM(L6:L3000)</f>
         <v>0</v>
       </c>
-      <c r="H1" s="26"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="10" t="s">
+      <c r="M1" s="19"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="18">
+      <c r="R1" s="19">
         <f>SUM(T6:T3000)</f>
         <v>0</v>
       </c>
-      <c r="S1" s="18"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
       <c r="V1" s="5"/>
       <c r="W1" s="5"/>
       <c r="X1" s="5"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="23" t="s">
+      <c r="Y1" s="7"/>
+      <c r="Z1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="AA1" s="23"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="19" t="s">
+      <c r="AA1" s="18"/>
+      <c r="AB1" s="7"/>
+      <c r="AC1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="19"/>
-      <c r="AE1" s="18">
+      <c r="AD1" s="26"/>
+      <c r="AE1" s="19">
         <f>SUM(AF6:AF3000)</f>
         <v>0</v>
       </c>
-      <c r="AF1" s="18"/>
-      <c r="AG1" s="18"/>
+      <c r="AF1" s="19"/>
+      <c r="AG1" s="19"/>
       <c r="AH1" s="5"/>
       <c r="AI1" s="5"/>
       <c r="AJ1" s="5"/>
-      <c r="AK1" s="12"/>
-      <c r="AL1" s="17" t="s">
+      <c r="AK1" s="10"/>
+      <c r="AL1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="18">
+      <c r="AM1" s="14"/>
+      <c r="AN1" s="19">
         <f>SUM(AO6:AO3000)</f>
         <v>0</v>
       </c>
-      <c r="AO1" s="18"/>
-      <c r="AP1" s="18"/>
-      <c r="AQ1" s="11"/>
+      <c r="AO1" s="19"/>
+      <c r="AP1" s="19"/>
+      <c r="AQ1" s="9"/>
       <c r="AR1" s="5"/>
       <c r="AS1" s="5"/>
-      <c r="AT1" s="12"/>
-      <c r="AU1" s="17" t="s">
+      <c r="AT1" s="10"/>
+      <c r="AU1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="AV1" s="17"/>
-      <c r="AW1" s="17"/>
-      <c r="AX1" s="18">
+      <c r="AV1" s="14"/>
+      <c r="AW1" s="14"/>
+      <c r="AX1" s="19">
         <f>SUM(AX6:AX3000)</f>
         <v>0</v>
       </c>
-      <c r="AY1" s="18"/>
-      <c r="AZ1" s="18"/>
+      <c r="AY1" s="19"/>
+      <c r="AZ1" s="19"/>
       <c r="BA1" s="5"/>
-      <c r="BD1" s="17" t="s">
+      <c r="BD1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="BE1" s="17"/>
-      <c r="BF1" s="17"/>
-      <c r="BG1" s="18">
+      <c r="BE1" s="14"/>
+      <c r="BF1" s="14"/>
+      <c r="BG1" s="19">
         <f>SUM(BG6:BG3000)</f>
         <v>0</v>
       </c>
-      <c r="BH1" s="18"/>
-      <c r="BI1" s="18"/>
+      <c r="BH1" s="19"/>
+      <c r="BI1" s="19"/>
       <c r="BJ1" s="5"/>
-      <c r="BM1" s="17" t="s">
+      <c r="BM1" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="BN1" s="17"/>
-      <c r="BO1" s="17"/>
-      <c r="BP1" s="18">
+      <c r="BN1" s="14"/>
+      <c r="BO1" s="14"/>
+      <c r="BP1" s="19">
         <f>SUM(BP6:BP3000)</f>
         <v>0</v>
       </c>
-      <c r="BQ1" s="18"/>
-      <c r="BR1" s="18"/>
+      <c r="BQ1" s="19"/>
+      <c r="BR1" s="19"/>
       <c r="BS1" s="5"/>
-      <c r="BV1" s="17" t="s">
+      <c r="BV1" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="BW1" s="17"/>
-      <c r="BX1" s="17"/>
-      <c r="BY1" s="18">
+      <c r="BW1" s="14"/>
+      <c r="BX1" s="14"/>
+      <c r="BY1" s="19">
         <f>SUM(BY6:BY3000)</f>
         <v>0</v>
       </c>
-      <c r="BZ1" s="18"/>
-      <c r="CA1" s="18"/>
+      <c r="BZ1" s="19"/>
+      <c r="CA1" s="19"/>
       <c r="CB1" s="5"/>
-      <c r="CE1" s="17" t="s">
+      <c r="CE1" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="CF1" s="17"/>
-      <c r="CG1" s="17"/>
-      <c r="CH1" s="18">
+      <c r="CF1" s="14"/>
+      <c r="CG1" s="14"/>
+      <c r="CH1" s="19">
         <f>SUM(CH6:CH3000)</f>
         <v>0</v>
       </c>
-      <c r="CI1" s="18"/>
-      <c r="CJ1" s="18"/>
+      <c r="CI1" s="19"/>
+      <c r="CJ1" s="19"/>
       <c r="CK1" s="5"/>
-      <c r="CN1" s="17" t="s">
+      <c r="CN1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="CO1" s="17"/>
-      <c r="CP1" s="17"/>
-      <c r="CQ1" s="18">
+      <c r="CO1" s="14"/>
+      <c r="CP1" s="14"/>
+      <c r="CQ1" s="19">
         <f>SUM(CQ6:CQ3000)</f>
         <v>0</v>
       </c>
-      <c r="CR1" s="18"/>
-      <c r="CS1" s="18"/>
+      <c r="CR1" s="19"/>
+      <c r="CS1" s="19"/>
       <c r="CT1" s="5"/>
     </row>
     <row r="2" spans="1:98" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20"/>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="21"/>
+      <c r="B2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="25" t="s">
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25">
+      <c r="K2" s="16"/>
+      <c r="L2" s="16">
         <f>SUM(O6:O3000)</f>
         <v>0</v>
       </c>
-      <c r="H2" s="25"/>
-      <c r="I2" s="3" t="str">
-        <f>IF(G2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
+      <c r="M2" s="16"/>
+      <c r="N2" s="3" t="str">
+        <f>IF(L2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
-      <c r="J2" s="14"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12" t="s">
+      <c r="O2" s="12"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="R2" s="17">
+      <c r="R2" s="14">
         <f>SUM(X6:X3000)</f>
         <v>0</v>
       </c>
-      <c r="S2" s="17"/>
+      <c r="S2" s="14"/>
       <c r="T2" s="3" t="str">
         <f>IF(R2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
-      <c r="U2" s="16"/>
+      <c r="U2" s="13"/>
       <c r="V2" s="3"/>
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
       <c r="Y2" s="5"/>
-      <c r="Z2" s="15" t="s">
+      <c r="Z2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="17" t="s">
+      <c r="AA2" s="12"/>
+      <c r="AB2" s="10"/>
+      <c r="AC2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="AD2" s="17"/>
-      <c r="AE2" s="17">
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14">
         <f>SUM(AI6:AI3000)</f>
         <v>0</v>
       </c>
-      <c r="AF2" s="17"/>
-      <c r="AG2" s="17"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
       <c r="AH2" s="3" t="str">
         <f>IF(AE2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
       <c r="AI2" s="5"/>
       <c r="AJ2" s="5"/>
-      <c r="AK2" s="12"/>
-      <c r="AL2" s="17" t="s">
+      <c r="AK2" s="10"/>
+      <c r="AL2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="AM2" s="17"/>
-      <c r="AN2" s="17">
+      <c r="AM2" s="14"/>
+      <c r="AN2" s="14">
         <f>SUM(AR6:AR3000)</f>
         <v>0</v>
       </c>
-      <c r="AO2" s="17"/>
-      <c r="AP2" s="17"/>
+      <c r="AO2" s="14"/>
+      <c r="AP2" s="14"/>
       <c r="AQ2" s="3" t="str">
         <f>IF(AN2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
       <c r="AR2" s="5"/>
       <c r="AS2" s="5"/>
-      <c r="AT2" s="12"/>
-      <c r="AU2" s="17" t="s">
+      <c r="AT2" s="10"/>
+      <c r="AU2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="AV2" s="17"/>
-      <c r="AW2" s="17"/>
-      <c r="AX2" s="17">
+      <c r="AV2" s="14"/>
+      <c r="AW2" s="14"/>
+      <c r="AX2" s="14">
         <f>SUM(BB6:BB3000)</f>
         <v>0</v>
       </c>
-      <c r="AY2" s="17"/>
-      <c r="AZ2" s="17"/>
+      <c r="AY2" s="14"/>
+      <c r="AZ2" s="14"/>
       <c r="BA2" s="3" t="str">
         <f>IF(AY2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
-      <c r="BD2" s="17" t="s">
+      <c r="BD2" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="BE2" s="17"/>
-      <c r="BF2" s="17"/>
-      <c r="BG2" s="17">
+      <c r="BE2" s="14"/>
+      <c r="BF2" s="14"/>
+      <c r="BG2" s="14">
         <f>SUM(BK6:BK3000)</f>
         <v>0</v>
       </c>
-      <c r="BH2" s="17"/>
-      <c r="BI2" s="17"/>
+      <c r="BH2" s="14"/>
+      <c r="BI2" s="14"/>
       <c r="BJ2" s="3" t="str">
         <f>IF(BH2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
-      <c r="BM2" s="17" t="s">
+      <c r="BM2" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="BN2" s="17"/>
-      <c r="BO2" s="17"/>
-      <c r="BP2" s="17">
+      <c r="BN2" s="14"/>
+      <c r="BO2" s="14"/>
+      <c r="BP2" s="14">
         <f>SUM(BT6:BT3000)</f>
         <v>0</v>
       </c>
-      <c r="BQ2" s="17"/>
-      <c r="BR2" s="17"/>
+      <c r="BQ2" s="14"/>
+      <c r="BR2" s="14"/>
       <c r="BS2" s="3" t="str">
         <f>IF(BQ2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
-      <c r="BV2" s="17" t="s">
+      <c r="BV2" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="BW2" s="17"/>
-      <c r="BX2" s="17"/>
-      <c r="BY2" s="17">
+      <c r="BW2" s="14"/>
+      <c r="BX2" s="14"/>
+      <c r="BY2" s="14">
         <f>SUM(CC6:CC3000)</f>
         <v>0</v>
       </c>
-      <c r="BZ2" s="17"/>
-      <c r="CA2" s="17"/>
+      <c r="BZ2" s="14"/>
+      <c r="CA2" s="14"/>
       <c r="CB2" s="3" t="str">
         <f>IF(BZ2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
-      <c r="CE2" s="17" t="s">
+      <c r="CE2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="CF2" s="17"/>
-      <c r="CG2" s="17"/>
-      <c r="CH2" s="17">
+      <c r="CF2" s="14"/>
+      <c r="CG2" s="14"/>
+      <c r="CH2" s="14">
         <f>SUM(CL6:CL3000)</f>
         <v>0</v>
       </c>
-      <c r="CI2" s="17"/>
-      <c r="CJ2" s="17"/>
+      <c r="CI2" s="14"/>
+      <c r="CJ2" s="14"/>
       <c r="CK2" s="3" t="str">
         <f>IF(CI2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
-      <c r="CN2" s="17" t="s">
+      <c r="CN2" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="CO2" s="17"/>
-      <c r="CP2" s="17"/>
-      <c r="CQ2" s="17">
+      <c r="CO2" s="14"/>
+      <c r="CP2" s="14"/>
+      <c r="CQ2" s="14">
         <f>SUM(CU6:CU3000)</f>
         <v>0</v>
       </c>
-      <c r="CR2" s="17"/>
-      <c r="CS2" s="17"/>
+      <c r="CR2" s="14"/>
+      <c r="CS2" s="14"/>
       <c r="CT2" s="3" t="str">
         <f>IF(CR2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
     </row>
     <row r="3" spans="1:98" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="13" t="s">
+      <c r="A3" s="21"/>
+      <c r="B3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="25" t="s">
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="25"/>
-      <c r="G3" s="28">
+      <c r="K3" s="16"/>
+      <c r="L3" s="15">
         <f>SUM(K6:K3000)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12" t="s">
+      <c r="M3" s="15"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="28">
+      <c r="R3" s="15">
         <f>SUM(S6:S3000)</f>
         <v>0</v>
       </c>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="15"/>
+      <c r="U3" s="15"/>
       <c r="V3" s="3"/>
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
       <c r="Y3" s="5"/>
-      <c r="Z3" s="15" t="s">
+      <c r="Z3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="AA3" s="15"/>
-      <c r="AB3" s="12"/>
-      <c r="AC3" s="17" t="s">
+      <c r="AA3" s="12"/>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="AD3" s="17"/>
-      <c r="AE3" s="17">
+      <c r="AD3" s="14"/>
+      <c r="AE3" s="14">
         <f>SUM(AE6:AE3000)</f>
         <v>0</v>
       </c>
-      <c r="AF3" s="17"/>
-      <c r="AG3" s="17"/>
+      <c r="AF3" s="14"/>
+      <c r="AG3" s="14"/>
       <c r="AH3" s="3"/>
       <c r="AI3" s="5"/>
       <c r="AJ3" s="5"/>
-      <c r="AK3" s="12"/>
-      <c r="AL3" s="17" t="s">
+      <c r="AK3" s="10"/>
+      <c r="AL3" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="AM3" s="17"/>
-      <c r="AN3" s="17">
+      <c r="AM3" s="14"/>
+      <c r="AN3" s="14">
         <f>SUM(AN6:AN3000)</f>
         <v>0</v>
       </c>
-      <c r="AO3" s="17"/>
-      <c r="AP3" s="17"/>
+      <c r="AO3" s="14"/>
+      <c r="AP3" s="14"/>
       <c r="AQ3" s="3"/>
       <c r="AR3" s="5"/>
       <c r="AS3" s="5"/>
-      <c r="AT3" s="12"/>
-      <c r="AU3" s="17" t="s">
+      <c r="AT3" s="10"/>
+      <c r="AU3" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="AV3" s="17"/>
-      <c r="AW3" s="17"/>
-      <c r="AX3" s="17">
+      <c r="AV3" s="14"/>
+      <c r="AW3" s="14"/>
+      <c r="AX3" s="14">
         <f>SUM(AW6:AW3000)</f>
         <v>0</v>
       </c>
-      <c r="AY3" s="17"/>
-      <c r="AZ3" s="17"/>
+      <c r="AY3" s="14"/>
+      <c r="AZ3" s="14"/>
       <c r="BA3" s="5"/>
-      <c r="BD3" s="17" t="s">
+      <c r="BD3" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="BE3" s="17"/>
-      <c r="BF3" s="17"/>
-      <c r="BG3" s="17">
+      <c r="BE3" s="14"/>
+      <c r="BF3" s="14"/>
+      <c r="BG3" s="14">
         <f>SUM(BF6:BF3000)</f>
         <v>0</v>
       </c>
-      <c r="BH3" s="17"/>
-      <c r="BI3" s="17"/>
+      <c r="BH3" s="14"/>
+      <c r="BI3" s="14"/>
       <c r="BJ3" s="5"/>
-      <c r="BM3" s="17" t="s">
+      <c r="BM3" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="BN3" s="17"/>
-      <c r="BO3" s="17"/>
-      <c r="BP3" s="17">
+      <c r="BN3" s="14"/>
+      <c r="BO3" s="14"/>
+      <c r="BP3" s="14">
         <f>SUM(BO6:BO3000)</f>
         <v>0</v>
       </c>
-      <c r="BQ3" s="17"/>
-      <c r="BR3" s="17"/>
+      <c r="BQ3" s="14"/>
+      <c r="BR3" s="14"/>
       <c r="BS3" s="5"/>
-      <c r="BV3" s="17" t="s">
+      <c r="BV3" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="BW3" s="17"/>
-      <c r="BX3" s="17"/>
-      <c r="BY3" s="17">
+      <c r="BW3" s="14"/>
+      <c r="BX3" s="14"/>
+      <c r="BY3" s="14">
         <f>SUM(BX6:BX3000)</f>
         <v>0</v>
       </c>
-      <c r="BZ3" s="17"/>
-      <c r="CA3" s="17"/>
+      <c r="BZ3" s="14"/>
+      <c r="CA3" s="14"/>
       <c r="CB3" s="5"/>
-      <c r="CE3" s="17" t="s">
+      <c r="CE3" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="CF3" s="17"/>
-      <c r="CG3" s="17"/>
-      <c r="CH3" s="17">
+      <c r="CF3" s="14"/>
+      <c r="CG3" s="14"/>
+      <c r="CH3" s="14">
         <f>SUM(CG6:CG3000)</f>
         <v>0</v>
       </c>
-      <c r="CI3" s="17"/>
-      <c r="CJ3" s="17"/>
+      <c r="CI3" s="14"/>
+      <c r="CJ3" s="14"/>
       <c r="CK3" s="5"/>
-      <c r="CN3" s="17" t="s">
+      <c r="CN3" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="CO3" s="17"/>
-      <c r="CP3" s="17"/>
-      <c r="CQ3" s="17">
+      <c r="CO3" s="14"/>
+      <c r="CP3" s="14"/>
+      <c r="CQ3" s="14">
         <f>SUM(CP6:CP3000)</f>
         <v>0</v>
       </c>
-      <c r="CR3" s="17"/>
-      <c r="CS3" s="17"/>
+      <c r="CR3" s="14"/>
+      <c r="CS3" s="14"/>
       <c r="CT3" s="5"/>
     </row>
     <row r="4" spans="1:98" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="25" t="s">
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="17"/>
-      <c r="U4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="10"/>
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
       <c r="Y4" s="5"/>
-      <c r="Z4" s="15" t="s">
+      <c r="Z4" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="AA4" s="15"/>
-      <c r="AB4" s="12"/>
-      <c r="AC4" s="17"/>
-      <c r="AD4" s="17"/>
-      <c r="AE4" s="17"/>
-      <c r="AF4" s="17"/>
-      <c r="AG4" s="12"/>
+      <c r="AA4" s="12"/>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="14"/>
+      <c r="AD4" s="14"/>
+      <c r="AE4" s="14"/>
+      <c r="AF4" s="14"/>
+      <c r="AG4" s="10"/>
       <c r="AH4" s="5"/>
       <c r="AI4" s="5"/>
       <c r="AJ4" s="5"/>
-      <c r="AK4" s="12"/>
-      <c r="AL4" s="17"/>
-      <c r="AM4" s="17"/>
-      <c r="AN4" s="17"/>
-      <c r="AO4" s="17"/>
-      <c r="AP4" s="12"/>
-      <c r="AQ4" s="12"/>
+      <c r="AK4" s="10"/>
+      <c r="AL4" s="14"/>
+      <c r="AM4" s="14"/>
+      <c r="AN4" s="14"/>
+      <c r="AO4" s="14"/>
+      <c r="AP4" s="10"/>
+      <c r="AQ4" s="10"/>
       <c r="AR4" s="5"/>
       <c r="AS4" s="5"/>
-      <c r="AT4" s="12"/>
-      <c r="AU4" s="17"/>
-      <c r="AV4" s="17"/>
-      <c r="AW4" s="17"/>
-      <c r="AX4" s="17"/>
-      <c r="AY4" s="12"/>
-      <c r="AZ4" s="12"/>
+      <c r="AT4" s="10"/>
+      <c r="AU4" s="14"/>
+      <c r="AV4" s="14"/>
+      <c r="AW4" s="14"/>
+      <c r="AX4" s="14"/>
+      <c r="AY4" s="10"/>
+      <c r="AZ4" s="10"/>
       <c r="BA4" s="5"/>
-      <c r="BD4" s="17"/>
-      <c r="BE4" s="17"/>
-      <c r="BF4" s="17"/>
-      <c r="BG4" s="17"/>
-      <c r="BH4" s="12"/>
-      <c r="BI4" s="12"/>
+      <c r="BD4" s="14"/>
+      <c r="BE4" s="14"/>
+      <c r="BF4" s="14"/>
+      <c r="BG4" s="14"/>
+      <c r="BH4" s="10"/>
+      <c r="BI4" s="10"/>
       <c r="BJ4" s="5"/>
-      <c r="BM4" s="17"/>
-      <c r="BN4" s="17"/>
-      <c r="BO4" s="17"/>
-      <c r="BP4" s="17"/>
-      <c r="BQ4" s="12"/>
-      <c r="BR4" s="12"/>
+      <c r="BM4" s="14"/>
+      <c r="BN4" s="14"/>
+      <c r="BO4" s="14"/>
+      <c r="BP4" s="14"/>
+      <c r="BQ4" s="10"/>
+      <c r="BR4" s="10"/>
       <c r="BS4" s="5"/>
-      <c r="BV4" s="17"/>
-      <c r="BW4" s="17"/>
-      <c r="BX4" s="17"/>
-      <c r="BY4" s="17"/>
-      <c r="BZ4" s="12"/>
-      <c r="CA4" s="12"/>
+      <c r="BV4" s="14"/>
+      <c r="BW4" s="14"/>
+      <c r="BX4" s="14"/>
+      <c r="BY4" s="14"/>
+      <c r="BZ4" s="10"/>
+      <c r="CA4" s="10"/>
       <c r="CB4" s="5"/>
-      <c r="CE4" s="17"/>
-      <c r="CF4" s="17"/>
-      <c r="CG4" s="17"/>
-      <c r="CH4" s="17"/>
-      <c r="CI4" s="12"/>
-      <c r="CJ4" s="12"/>
+      <c r="CE4" s="14"/>
+      <c r="CF4" s="14"/>
+      <c r="CG4" s="14"/>
+      <c r="CH4" s="14"/>
+      <c r="CI4" s="10"/>
+      <c r="CJ4" s="10"/>
       <c r="CK4" s="5"/>
-      <c r="CN4" s="17"/>
-      <c r="CO4" s="17"/>
-      <c r="CP4" s="17"/>
-      <c r="CQ4" s="17"/>
-      <c r="CR4" s="12"/>
-      <c r="CS4" s="12"/>
+      <c r="CN4" s="14"/>
+      <c r="CO4" s="14"/>
+      <c r="CP4" s="14"/>
+      <c r="CQ4" s="14"/>
+      <c r="CR4" s="10"/>
+      <c r="CS4" s="10"/>
       <c r="CT4" s="5"/>
     </row>
     <row r="5" spans="1:98" s="2" customFormat="1" ht="63" x14ac:dyDescent="0.25">
@@ -1574,56 +1588,21 @@
       <c r="CT5" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="77">
-    <mergeCell ref="AC4:AF4"/>
-    <mergeCell ref="AL4:AO4"/>
-    <mergeCell ref="AU4:AX4"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="Q4:T4"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE2:AG2"/>
-    <mergeCell ref="AE3:AG3"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AL2:AM2"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="AN2:AP2"/>
-    <mergeCell ref="AN3:AP3"/>
-    <mergeCell ref="AN1:AP1"/>
-    <mergeCell ref="BD4:BG4"/>
-    <mergeCell ref="AX1:AZ1"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AU3:AW3"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="AX3:AZ3"/>
-    <mergeCell ref="AU1:AW1"/>
-    <mergeCell ref="BD1:BF1"/>
-    <mergeCell ref="BG1:BI1"/>
-    <mergeCell ref="BD2:BF2"/>
-    <mergeCell ref="BG2:BI2"/>
-    <mergeCell ref="BD3:BF3"/>
-    <mergeCell ref="BG3:BI3"/>
+  <mergeCells count="82">
+    <mergeCell ref="CN4:CQ4"/>
+    <mergeCell ref="CN1:CP1"/>
+    <mergeCell ref="CQ1:CS1"/>
+    <mergeCell ref="CN2:CP2"/>
+    <mergeCell ref="CQ2:CS2"/>
+    <mergeCell ref="CN3:CP3"/>
+    <mergeCell ref="CQ3:CS3"/>
+    <mergeCell ref="CE4:CH4"/>
+    <mergeCell ref="CE1:CG1"/>
+    <mergeCell ref="CH1:CJ1"/>
+    <mergeCell ref="CE2:CG2"/>
+    <mergeCell ref="CH2:CJ2"/>
+    <mergeCell ref="CE3:CG3"/>
+    <mergeCell ref="CH3:CJ3"/>
     <mergeCell ref="BM4:BP4"/>
     <mergeCell ref="BV1:BX1"/>
     <mergeCell ref="BY1:CA1"/>
@@ -1638,22 +1617,67 @@
     <mergeCell ref="BP2:BR2"/>
     <mergeCell ref="BM3:BO3"/>
     <mergeCell ref="BP3:BR3"/>
-    <mergeCell ref="CE4:CH4"/>
-    <mergeCell ref="CE1:CG1"/>
-    <mergeCell ref="CH1:CJ1"/>
-    <mergeCell ref="CE2:CG2"/>
-    <mergeCell ref="CH2:CJ2"/>
-    <mergeCell ref="CE3:CG3"/>
-    <mergeCell ref="CH3:CJ3"/>
-    <mergeCell ref="CN4:CQ4"/>
-    <mergeCell ref="CN1:CP1"/>
-    <mergeCell ref="CQ1:CS1"/>
-    <mergeCell ref="CN2:CP2"/>
-    <mergeCell ref="CQ2:CS2"/>
-    <mergeCell ref="CN3:CP3"/>
-    <mergeCell ref="CQ3:CS3"/>
+    <mergeCell ref="BD4:BG4"/>
+    <mergeCell ref="AX1:AZ1"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AU3:AW3"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="AX3:AZ3"/>
+    <mergeCell ref="AU1:AW1"/>
+    <mergeCell ref="BD1:BF1"/>
+    <mergeCell ref="BG1:BI1"/>
+    <mergeCell ref="BD2:BF2"/>
+    <mergeCell ref="BG2:BI2"/>
+    <mergeCell ref="BD3:BF3"/>
+    <mergeCell ref="BG3:BI3"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AL2:AM2"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="AN2:AP2"/>
+    <mergeCell ref="AN3:AP3"/>
+    <mergeCell ref="AN1:AP1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="AE3:AG3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="AC4:AF4"/>
+    <mergeCell ref="AL4:AO4"/>
+    <mergeCell ref="AU4:AX4"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="T3:U3"/>
   </mergeCells>
   <conditionalFormatting sqref="G2">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThanOrEqual">
+      <formula>42001</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>42001</formula>
     </cfRule>

--- a/format_excel/Ware_Gen_clean.xlsx
+++ b/format_excel/Ware_Gen_clean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://atvtireinc-my.sharepoint.com/personal/vjdelrosario_avatco_com/Documents/Desktop/MWF Offers/format_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="511" documentId="11_F25DC773A252ABDACC1048891919571A5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{648991D6-EAA3-42BB-8FB9-2AD4213881F6}"/>
+  <xr:revisionPtr revIDLastSave="517" documentId="11_F25DC773A252ABDACC1048891919571A5BDE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACCCE852-98D8-4D37-9F6A-EC2879888884}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -208,30 +208,30 @@
 Hand Inventory</t>
   </si>
   <si>
-    <t>Winchester, Tenesse TOTAL AMOUNT LOAD:</t>
-  </si>
-  <si>
-    <t>Winchester, Tennesse Total Weight (full load met at 42k lbs):</t>
-  </si>
-  <si>
-    <t>Winchester, Tennesse Total Piece Count:</t>
-  </si>
-  <si>
     <t>Winchester, Tennesse On
 Hand Inventory</t>
   </si>
   <si>
-    <t>Winchester, Kentucky TOTAL AMOUNT LOAD:</t>
-  </si>
-  <si>
-    <t>Winchester, Kentucky Total Weight (full load met at 42k lbs):</t>
-  </si>
-  <si>
-    <t>Winchester, Kentucky Total Piece Count:</t>
-  </si>
-  <si>
     <t>Winchester, Kentucky On
 Hand Inventory</t>
+  </si>
+  <si>
+    <t>Winchester, KY Total Weight (full load met at 42k lbs):</t>
+  </si>
+  <si>
+    <t>Winchester, KY TOTAL AMOUNT LOAD:</t>
+  </si>
+  <si>
+    <t>Winchester, TN TOTAL AMOUNT LOAD:</t>
+  </si>
+  <si>
+    <t>Winchester, TN Total Weight (full load met at 42k lbs):</t>
+  </si>
+  <si>
+    <t>Winchester, TN Total Piece Count:</t>
+  </si>
+  <si>
+    <t>Winchester, KY Total Piece Count:</t>
   </si>
 </sst>
 </file>
@@ -379,47 +379,47 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -796,14 +796,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:98" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22" t="s">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="23"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="20"/>
       <c r="E1" s="25"/>
       <c r="F1" s="25"/>
       <c r="G1" s="24"/>
@@ -813,155 +813,155 @@
         <v>2</v>
       </c>
       <c r="K1" s="25"/>
-      <c r="L1" s="19">
+      <c r="L1" s="16">
         <f>SUM(L6:L3000)</f>
         <v>0</v>
       </c>
-      <c r="M1" s="19"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
       <c r="P1" s="7"/>
       <c r="Q1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="19">
+      <c r="R1" s="16">
         <f>SUM(T6:T3000)</f>
         <v>0</v>
       </c>
-      <c r="S1" s="19"/>
+      <c r="S1" s="16"/>
       <c r="T1" s="9"/>
       <c r="U1" s="9"/>
       <c r="V1" s="5"/>
       <c r="W1" s="5"/>
       <c r="X1" s="5"/>
       <c r="Y1" s="7"/>
-      <c r="Z1" s="18" t="s">
+      <c r="Z1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="AA1" s="18"/>
+      <c r="AA1" s="21"/>
       <c r="AB1" s="7"/>
-      <c r="AC1" s="26" t="s">
+      <c r="AC1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="26"/>
-      <c r="AE1" s="19">
+      <c r="AD1" s="17"/>
+      <c r="AE1" s="16">
         <f>SUM(AF6:AF3000)</f>
         <v>0</v>
       </c>
-      <c r="AF1" s="19"/>
-      <c r="AG1" s="19"/>
+      <c r="AF1" s="16"/>
+      <c r="AG1" s="16"/>
       <c r="AH1" s="5"/>
       <c r="AI1" s="5"/>
       <c r="AJ1" s="5"/>
       <c r="AK1" s="10"/>
-      <c r="AL1" s="14" t="s">
+      <c r="AL1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AM1" s="14"/>
-      <c r="AN1" s="19">
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="16">
         <f>SUM(AO6:AO3000)</f>
         <v>0</v>
       </c>
-      <c r="AO1" s="19"/>
-      <c r="AP1" s="19"/>
+      <c r="AO1" s="16"/>
+      <c r="AP1" s="16"/>
       <c r="AQ1" s="9"/>
       <c r="AR1" s="5"/>
       <c r="AS1" s="5"/>
       <c r="AT1" s="10"/>
-      <c r="AU1" s="14" t="s">
+      <c r="AU1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="AV1" s="14"/>
-      <c r="AW1" s="14"/>
-      <c r="AX1" s="19">
+      <c r="AV1" s="15"/>
+      <c r="AW1" s="15"/>
+      <c r="AX1" s="16">
         <f>SUM(AX6:AX3000)</f>
         <v>0</v>
       </c>
-      <c r="AY1" s="19"/>
-      <c r="AZ1" s="19"/>
+      <c r="AY1" s="16"/>
+      <c r="AZ1" s="16"/>
       <c r="BA1" s="5"/>
-      <c r="BD1" s="14" t="s">
+      <c r="BD1" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="BE1" s="14"/>
-      <c r="BF1" s="14"/>
-      <c r="BG1" s="19">
+      <c r="BE1" s="15"/>
+      <c r="BF1" s="15"/>
+      <c r="BG1" s="16">
         <f>SUM(BG6:BG3000)</f>
         <v>0</v>
       </c>
-      <c r="BH1" s="19"/>
-      <c r="BI1" s="19"/>
+      <c r="BH1" s="16"/>
+      <c r="BI1" s="16"/>
       <c r="BJ1" s="5"/>
-      <c r="BM1" s="14" t="s">
+      <c r="BM1" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="BN1" s="15"/>
+      <c r="BO1" s="15"/>
+      <c r="BP1" s="16">
+        <f>SUM(BP6:BP3000)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ1" s="16"/>
+      <c r="BR1" s="16"/>
+      <c r="BS1" s="5"/>
+      <c r="BV1" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="BW1" s="15"/>
+      <c r="BX1" s="15"/>
+      <c r="BY1" s="16">
+        <f>SUM(BY6:BY3000)</f>
+        <v>0</v>
+      </c>
+      <c r="BZ1" s="16"/>
+      <c r="CA1" s="16"/>
+      <c r="CB1" s="5"/>
+      <c r="CE1" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="CF1" s="15"/>
+      <c r="CG1" s="15"/>
+      <c r="CH1" s="16">
+        <f>SUM(CH6:CH3000)</f>
+        <v>0</v>
+      </c>
+      <c r="CI1" s="16"/>
+      <c r="CJ1" s="16"/>
+      <c r="CK1" s="5"/>
+      <c r="CN1" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="BN1" s="14"/>
-      <c r="BO1" s="14"/>
-      <c r="BP1" s="19">
-        <f>SUM(BP6:BP3000)</f>
-        <v>0</v>
-      </c>
-      <c r="BQ1" s="19"/>
-      <c r="BR1" s="19"/>
-      <c r="BS1" s="5"/>
-      <c r="BV1" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="BW1" s="14"/>
-      <c r="BX1" s="14"/>
-      <c r="BY1" s="19">
-        <f>SUM(BY6:BY3000)</f>
-        <v>0</v>
-      </c>
-      <c r="BZ1" s="19"/>
-      <c r="CA1" s="19"/>
-      <c r="CB1" s="5"/>
-      <c r="CE1" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="CF1" s="14"/>
-      <c r="CG1" s="14"/>
-      <c r="CH1" s="19">
-        <f>SUM(CH6:CH3000)</f>
-        <v>0</v>
-      </c>
-      <c r="CI1" s="19"/>
-      <c r="CJ1" s="19"/>
-      <c r="CK1" s="5"/>
-      <c r="CN1" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="CO1" s="14"/>
-      <c r="CP1" s="14"/>
-      <c r="CQ1" s="19">
+      <c r="CO1" s="15"/>
+      <c r="CP1" s="15"/>
+      <c r="CQ1" s="16">
         <f>SUM(CQ6:CQ3000)</f>
         <v>0</v>
       </c>
-      <c r="CR1" s="19"/>
-      <c r="CS1" s="19"/>
+      <c r="CR1" s="16"/>
+      <c r="CS1" s="16"/>
       <c r="CT1" s="5"/>
     </row>
     <row r="2" spans="1:98" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21"/>
+      <c r="A2" s="18"/>
       <c r="B2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
       <c r="I2" s="3"/>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16">
+      <c r="K2" s="23"/>
+      <c r="L2" s="23">
         <f>SUM(O6:O3000)</f>
         <v>0</v>
       </c>
-      <c r="M2" s="16"/>
+      <c r="M2" s="23"/>
       <c r="N2" s="3" t="str">
         <f>IF(L2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
@@ -971,11 +971,11 @@
       <c r="Q2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="R2" s="14">
+      <c r="R2" s="15">
         <f>SUM(X6:X3000)</f>
         <v>0</v>
       </c>
-      <c r="S2" s="14"/>
+      <c r="S2" s="15"/>
       <c r="T2" s="3" t="str">
         <f>IF(R2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
@@ -990,16 +990,16 @@
       </c>
       <c r="AA2" s="12"/>
       <c r="AB2" s="10"/>
-      <c r="AC2" s="14" t="s">
+      <c r="AC2" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="AD2" s="14"/>
-      <c r="AE2" s="14">
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15">
         <f>SUM(AI6:AI3000)</f>
         <v>0</v>
       </c>
-      <c r="AF2" s="14"/>
-      <c r="AG2" s="14"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
       <c r="AH2" s="3" t="str">
         <f>IF(AE2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
@@ -1007,16 +1007,16 @@
       <c r="AI2" s="5"/>
       <c r="AJ2" s="5"/>
       <c r="AK2" s="10"/>
-      <c r="AL2" s="14" t="s">
+      <c r="AL2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="AM2" s="14"/>
-      <c r="AN2" s="14">
+      <c r="AM2" s="15"/>
+      <c r="AN2" s="15">
         <f>SUM(AR6:AR3000)</f>
         <v>0</v>
       </c>
-      <c r="AO2" s="14"/>
-      <c r="AP2" s="14"/>
+      <c r="AO2" s="15"/>
+      <c r="AP2" s="15"/>
       <c r="AQ2" s="3" t="str">
         <f>IF(AN2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
@@ -1024,131 +1024,131 @@
       <c r="AR2" s="5"/>
       <c r="AS2" s="5"/>
       <c r="AT2" s="10"/>
-      <c r="AU2" s="14" t="s">
+      <c r="AU2" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="AV2" s="14"/>
-      <c r="AW2" s="14"/>
-      <c r="AX2" s="14">
+      <c r="AV2" s="15"/>
+      <c r="AW2" s="15"/>
+      <c r="AX2" s="15">
         <f>SUM(BB6:BB3000)</f>
         <v>0</v>
       </c>
-      <c r="AY2" s="14"/>
-      <c r="AZ2" s="14"/>
+      <c r="AY2" s="15"/>
+      <c r="AZ2" s="15"/>
       <c r="BA2" s="3" t="str">
         <f>IF(AY2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
-      <c r="BD2" s="14" t="s">
+      <c r="BD2" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="BE2" s="14"/>
-      <c r="BF2" s="14"/>
-      <c r="BG2" s="14">
+      <c r="BE2" s="15"/>
+      <c r="BF2" s="15"/>
+      <c r="BG2" s="15">
         <f>SUM(BK6:BK3000)</f>
         <v>0</v>
       </c>
-      <c r="BH2" s="14"/>
-      <c r="BI2" s="14"/>
+      <c r="BH2" s="15"/>
+      <c r="BI2" s="15"/>
       <c r="BJ2" s="3" t="str">
         <f>IF(BH2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
-      <c r="BM2" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="BN2" s="14"/>
-      <c r="BO2" s="14"/>
-      <c r="BP2" s="14">
+      <c r="BM2" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="BN2" s="15"/>
+      <c r="BO2" s="15"/>
+      <c r="BP2" s="15">
         <f>SUM(BT6:BT3000)</f>
         <v>0</v>
       </c>
-      <c r="BQ2" s="14"/>
-      <c r="BR2" s="14"/>
+      <c r="BQ2" s="15"/>
+      <c r="BR2" s="15"/>
       <c r="BS2" s="3" t="str">
         <f>IF(BQ2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
-      <c r="BV2" s="14" t="s">
+      <c r="BV2" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="BW2" s="14"/>
-      <c r="BX2" s="14"/>
-      <c r="BY2" s="14">
+      <c r="BW2" s="15"/>
+      <c r="BX2" s="15"/>
+      <c r="BY2" s="15">
         <f>SUM(CC6:CC3000)</f>
         <v>0</v>
       </c>
-      <c r="BZ2" s="14"/>
-      <c r="CA2" s="14"/>
+      <c r="BZ2" s="15"/>
+      <c r="CA2" s="15"/>
       <c r="CB2" s="3" t="str">
         <f>IF(BZ2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
-      <c r="CE2" s="14" t="s">
+      <c r="CE2" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="CF2" s="14"/>
-      <c r="CG2" s="14"/>
-      <c r="CH2" s="14">
+      <c r="CF2" s="15"/>
+      <c r="CG2" s="15"/>
+      <c r="CH2" s="15">
         <f>SUM(CL6:CL3000)</f>
         <v>0</v>
       </c>
-      <c r="CI2" s="14"/>
-      <c r="CJ2" s="14"/>
+      <c r="CI2" s="15"/>
+      <c r="CJ2" s="15"/>
       <c r="CK2" s="3" t="str">
         <f>IF(CI2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
-      <c r="CN2" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="CO2" s="14"/>
-      <c r="CP2" s="14"/>
-      <c r="CQ2" s="14">
+      <c r="CN2" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="CO2" s="15"/>
+      <c r="CP2" s="15"/>
+      <c r="CQ2" s="15">
         <f>SUM(CU6:CU3000)</f>
         <v>0</v>
       </c>
-      <c r="CR2" s="14"/>
-      <c r="CS2" s="14"/>
+      <c r="CR2" s="15"/>
+      <c r="CS2" s="15"/>
       <c r="CT2" s="3" t="str">
         <f>IF(CR2&gt;42000,"WEIGHT EXCEEDS LIMIT, PLEASE ASSIGN CUT ITEM","WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM")</f>
         <v>WEIGHT UNDER LIMIT, PLEASE ASSIGN FILL ITEM</v>
       </c>
     </row>
     <row r="3" spans="1:98" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21"/>
+      <c r="A3" s="18"/>
       <c r="B3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="16" t="s">
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="16"/>
-      <c r="L3" s="15">
+      <c r="K3" s="23"/>
+      <c r="L3" s="26">
         <f>SUM(K6:K3000)</f>
         <v>0</v>
       </c>
-      <c r="M3" s="15"/>
+      <c r="M3" s="26"/>
       <c r="N3" s="12"/>
       <c r="O3" s="12"/>
       <c r="P3" s="10"/>
       <c r="Q3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="26">
         <f>SUM(S6:S3000)</f>
         <v>0</v>
       </c>
-      <c r="S3" s="15"/>
-      <c r="T3" s="15"/>
-      <c r="U3" s="15"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
       <c r="V3" s="3"/>
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
@@ -1158,105 +1158,105 @@
       </c>
       <c r="AA3" s="12"/>
       <c r="AB3" s="10"/>
-      <c r="AC3" s="14" t="s">
+      <c r="AC3" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14">
+      <c r="AD3" s="15"/>
+      <c r="AE3" s="15">
         <f>SUM(AE6:AE3000)</f>
         <v>0</v>
       </c>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="14"/>
+      <c r="AF3" s="15"/>
+      <c r="AG3" s="15"/>
       <c r="AH3" s="3"/>
       <c r="AI3" s="5"/>
       <c r="AJ3" s="5"/>
       <c r="AK3" s="10"/>
-      <c r="AL3" s="14" t="s">
+      <c r="AL3" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="AM3" s="14"/>
-      <c r="AN3" s="14">
+      <c r="AM3" s="15"/>
+      <c r="AN3" s="15">
         <f>SUM(AN6:AN3000)</f>
         <v>0</v>
       </c>
-      <c r="AO3" s="14"/>
-      <c r="AP3" s="14"/>
+      <c r="AO3" s="15"/>
+      <c r="AP3" s="15"/>
       <c r="AQ3" s="3"/>
       <c r="AR3" s="5"/>
       <c r="AS3" s="5"/>
       <c r="AT3" s="10"/>
-      <c r="AU3" s="14" t="s">
+      <c r="AU3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="AV3" s="14"/>
-      <c r="AW3" s="14"/>
-      <c r="AX3" s="14">
+      <c r="AV3" s="15"/>
+      <c r="AW3" s="15"/>
+      <c r="AX3" s="15">
         <f>SUM(AW6:AW3000)</f>
         <v>0</v>
       </c>
-      <c r="AY3" s="14"/>
-      <c r="AZ3" s="14"/>
+      <c r="AY3" s="15"/>
+      <c r="AZ3" s="15"/>
       <c r="BA3" s="5"/>
-      <c r="BD3" s="14" t="s">
+      <c r="BD3" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="BE3" s="14"/>
-      <c r="BF3" s="14"/>
-      <c r="BG3" s="14">
+      <c r="BE3" s="15"/>
+      <c r="BF3" s="15"/>
+      <c r="BG3" s="15">
         <f>SUM(BF6:BF3000)</f>
         <v>0</v>
       </c>
-      <c r="BH3" s="14"/>
-      <c r="BI3" s="14"/>
+      <c r="BH3" s="15"/>
+      <c r="BI3" s="15"/>
       <c r="BJ3" s="5"/>
-      <c r="BM3" s="14" t="s">
+      <c r="BM3" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="BN3" s="15"/>
+      <c r="BO3" s="15"/>
+      <c r="BP3" s="15">
+        <f>SUM(BO6:BO3000)</f>
+        <v>0</v>
+      </c>
+      <c r="BQ3" s="15"/>
+      <c r="BR3" s="15"/>
+      <c r="BS3" s="5"/>
+      <c r="BV3" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="BW3" s="15"/>
+      <c r="BX3" s="15"/>
+      <c r="BY3" s="15">
+        <f>SUM(BX6:BX3000)</f>
+        <v>0</v>
+      </c>
+      <c r="BZ3" s="15"/>
+      <c r="CA3" s="15"/>
+      <c r="CB3" s="5"/>
+      <c r="CE3" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="CF3" s="15"/>
+      <c r="CG3" s="15"/>
+      <c r="CH3" s="15">
+        <f>SUM(CG6:CG3000)</f>
+        <v>0</v>
+      </c>
+      <c r="CI3" s="15"/>
+      <c r="CJ3" s="15"/>
+      <c r="CK3" s="5"/>
+      <c r="CN3" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="BN3" s="14"/>
-      <c r="BO3" s="14"/>
-      <c r="BP3" s="14">
-        <f>SUM(BO6:BO3000)</f>
-        <v>0</v>
-      </c>
-      <c r="BQ3" s="14"/>
-      <c r="BR3" s="14"/>
-      <c r="BS3" s="5"/>
-      <c r="BV3" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="BW3" s="14"/>
-      <c r="BX3" s="14"/>
-      <c r="BY3" s="14">
-        <f>SUM(BX6:BX3000)</f>
-        <v>0</v>
-      </c>
-      <c r="BZ3" s="14"/>
-      <c r="CA3" s="14"/>
-      <c r="CB3" s="5"/>
-      <c r="CE3" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="CF3" s="14"/>
-      <c r="CG3" s="14"/>
-      <c r="CH3" s="14">
-        <f>SUM(CG6:CG3000)</f>
-        <v>0</v>
-      </c>
-      <c r="CI3" s="14"/>
-      <c r="CJ3" s="14"/>
-      <c r="CK3" s="5"/>
-      <c r="CN3" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="CO3" s="14"/>
-      <c r="CP3" s="14"/>
-      <c r="CQ3" s="14">
+      <c r="CO3" s="15"/>
+      <c r="CP3" s="15"/>
+      <c r="CQ3" s="15">
         <f>SUM(CP6:CP3000)</f>
         <v>0</v>
       </c>
-      <c r="CR3" s="14"/>
-      <c r="CS3" s="14"/>
+      <c r="CR3" s="15"/>
+      <c r="CS3" s="15"/>
       <c r="CT3" s="5"/>
     </row>
     <row r="4" spans="1:98" ht="17.25" x14ac:dyDescent="0.25">
@@ -1264,26 +1264,26 @@
       <c r="B4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="16" t="s">
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="12"/>
       <c r="O4" s="12"/>
       <c r="P4" s="10"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
       <c r="U4" s="10"/>
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
@@ -1294,63 +1294,63 @@
       </c>
       <c r="AA4" s="12"/>
       <c r="AB4" s="10"/>
-      <c r="AC4" s="14"/>
-      <c r="AD4" s="14"/>
-      <c r="AE4" s="14"/>
-      <c r="AF4" s="14"/>
+      <c r="AC4" s="15"/>
+      <c r="AD4" s="15"/>
+      <c r="AE4" s="15"/>
+      <c r="AF4" s="15"/>
       <c r="AG4" s="10"/>
       <c r="AH4" s="5"/>
       <c r="AI4" s="5"/>
       <c r="AJ4" s="5"/>
       <c r="AK4" s="10"/>
-      <c r="AL4" s="14"/>
-      <c r="AM4" s="14"/>
-      <c r="AN4" s="14"/>
-      <c r="AO4" s="14"/>
+      <c r="AL4" s="15"/>
+      <c r="AM4" s="15"/>
+      <c r="AN4" s="15"/>
+      <c r="AO4" s="15"/>
       <c r="AP4" s="10"/>
       <c r="AQ4" s="10"/>
       <c r="AR4" s="5"/>
       <c r="AS4" s="5"/>
       <c r="AT4" s="10"/>
-      <c r="AU4" s="14"/>
-      <c r="AV4" s="14"/>
-      <c r="AW4" s="14"/>
-      <c r="AX4" s="14"/>
+      <c r="AU4" s="15"/>
+      <c r="AV4" s="15"/>
+      <c r="AW4" s="15"/>
+      <c r="AX4" s="15"/>
       <c r="AY4" s="10"/>
       <c r="AZ4" s="10"/>
       <c r="BA4" s="5"/>
-      <c r="BD4" s="14"/>
-      <c r="BE4" s="14"/>
-      <c r="BF4" s="14"/>
-      <c r="BG4" s="14"/>
+      <c r="BD4" s="15"/>
+      <c r="BE4" s="15"/>
+      <c r="BF4" s="15"/>
+      <c r="BG4" s="15"/>
       <c r="BH4" s="10"/>
       <c r="BI4" s="10"/>
       <c r="BJ4" s="5"/>
-      <c r="BM4" s="14"/>
-      <c r="BN4" s="14"/>
-      <c r="BO4" s="14"/>
-      <c r="BP4" s="14"/>
+      <c r="BM4" s="15"/>
+      <c r="BN4" s="15"/>
+      <c r="BO4" s="15"/>
+      <c r="BP4" s="15"/>
       <c r="BQ4" s="10"/>
       <c r="BR4" s="10"/>
       <c r="BS4" s="5"/>
-      <c r="BV4" s="14"/>
-      <c r="BW4" s="14"/>
-      <c r="BX4" s="14"/>
-      <c r="BY4" s="14"/>
+      <c r="BV4" s="15"/>
+      <c r="BW4" s="15"/>
+      <c r="BX4" s="15"/>
+      <c r="BY4" s="15"/>
       <c r="BZ4" s="10"/>
       <c r="CA4" s="10"/>
       <c r="CB4" s="5"/>
-      <c r="CE4" s="14"/>
-      <c r="CF4" s="14"/>
-      <c r="CG4" s="14"/>
-      <c r="CH4" s="14"/>
+      <c r="CE4" s="15"/>
+      <c r="CF4" s="15"/>
+      <c r="CG4" s="15"/>
+      <c r="CH4" s="15"/>
       <c r="CI4" s="10"/>
       <c r="CJ4" s="10"/>
       <c r="CK4" s="5"/>
-      <c r="CN4" s="14"/>
-      <c r="CO4" s="14"/>
-      <c r="CP4" s="14"/>
-      <c r="CQ4" s="14"/>
+      <c r="CN4" s="15"/>
+      <c r="CO4" s="15"/>
+      <c r="CP4" s="15"/>
+      <c r="CQ4" s="15"/>
       <c r="CR4" s="10"/>
       <c r="CS4" s="10"/>
       <c r="CT4" s="5"/>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="BJ5" s="5"/>
       <c r="BM5" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="BN5" s="4" t="s">
         <v>31</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="CK5" s="5"/>
       <c r="CN5" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="CO5" s="4" t="s">
         <v>31</v>
@@ -1589,59 +1589,19 @@
     </row>
   </sheetData>
   <mergeCells count="82">
-    <mergeCell ref="CN4:CQ4"/>
-    <mergeCell ref="CN1:CP1"/>
-    <mergeCell ref="CQ1:CS1"/>
-    <mergeCell ref="CN2:CP2"/>
-    <mergeCell ref="CQ2:CS2"/>
-    <mergeCell ref="CN3:CP3"/>
-    <mergeCell ref="CQ3:CS3"/>
-    <mergeCell ref="CE4:CH4"/>
-    <mergeCell ref="CE1:CG1"/>
-    <mergeCell ref="CH1:CJ1"/>
-    <mergeCell ref="CE2:CG2"/>
-    <mergeCell ref="CH2:CJ2"/>
-    <mergeCell ref="CE3:CG3"/>
-    <mergeCell ref="CH3:CJ3"/>
-    <mergeCell ref="BM4:BP4"/>
-    <mergeCell ref="BV1:BX1"/>
-    <mergeCell ref="BY1:CA1"/>
-    <mergeCell ref="BV2:BX2"/>
-    <mergeCell ref="BY2:CA2"/>
-    <mergeCell ref="BV3:BX3"/>
-    <mergeCell ref="BY3:CA3"/>
-    <mergeCell ref="BV4:BY4"/>
-    <mergeCell ref="BM1:BO1"/>
-    <mergeCell ref="BP1:BR1"/>
-    <mergeCell ref="BM2:BO2"/>
-    <mergeCell ref="BP2:BR2"/>
-    <mergeCell ref="BM3:BO3"/>
-    <mergeCell ref="BP3:BR3"/>
-    <mergeCell ref="BD4:BG4"/>
-    <mergeCell ref="AX1:AZ1"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AU3:AW3"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="AX3:AZ3"/>
-    <mergeCell ref="AU1:AW1"/>
-    <mergeCell ref="BD1:BF1"/>
-    <mergeCell ref="BG1:BI1"/>
-    <mergeCell ref="BD2:BF2"/>
-    <mergeCell ref="BG2:BI2"/>
-    <mergeCell ref="BD3:BF3"/>
-    <mergeCell ref="BG3:BI3"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AL2:AM2"/>
-    <mergeCell ref="AL3:AM3"/>
-    <mergeCell ref="AN2:AP2"/>
-    <mergeCell ref="AN3:AP3"/>
-    <mergeCell ref="AN1:AP1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE2:AG2"/>
-    <mergeCell ref="AE3:AG3"/>
+    <mergeCell ref="AC4:AF4"/>
+    <mergeCell ref="AL4:AO4"/>
+    <mergeCell ref="AU4:AX4"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="T3:U3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="N1:O1"/>
@@ -1658,19 +1618,59 @@
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="L1:M1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="Q4:T4"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="AC4:AF4"/>
-    <mergeCell ref="AL4:AO4"/>
-    <mergeCell ref="AU4:AX4"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="AE3:AG3"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AL2:AM2"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="AN2:AP2"/>
+    <mergeCell ref="AN3:AP3"/>
+    <mergeCell ref="AN1:AP1"/>
+    <mergeCell ref="BD4:BG4"/>
+    <mergeCell ref="AX1:AZ1"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AU3:AW3"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="AX3:AZ3"/>
+    <mergeCell ref="AU1:AW1"/>
+    <mergeCell ref="BD1:BF1"/>
+    <mergeCell ref="BG1:BI1"/>
+    <mergeCell ref="BD2:BF2"/>
+    <mergeCell ref="BG2:BI2"/>
+    <mergeCell ref="BD3:BF3"/>
+    <mergeCell ref="BG3:BI3"/>
+    <mergeCell ref="BM4:BP4"/>
+    <mergeCell ref="BV1:BX1"/>
+    <mergeCell ref="BY1:CA1"/>
+    <mergeCell ref="BV2:BX2"/>
+    <mergeCell ref="BY2:CA2"/>
+    <mergeCell ref="BV3:BX3"/>
+    <mergeCell ref="BY3:CA3"/>
+    <mergeCell ref="BV4:BY4"/>
+    <mergeCell ref="BM1:BO1"/>
+    <mergeCell ref="BP1:BR1"/>
+    <mergeCell ref="BM2:BO2"/>
+    <mergeCell ref="BP2:BR2"/>
+    <mergeCell ref="BM3:BO3"/>
+    <mergeCell ref="BP3:BR3"/>
+    <mergeCell ref="CE4:CH4"/>
+    <mergeCell ref="CE1:CG1"/>
+    <mergeCell ref="CH1:CJ1"/>
+    <mergeCell ref="CE2:CG2"/>
+    <mergeCell ref="CH2:CJ2"/>
+    <mergeCell ref="CE3:CG3"/>
+    <mergeCell ref="CH3:CJ3"/>
+    <mergeCell ref="CN4:CQ4"/>
+    <mergeCell ref="CN1:CP1"/>
+    <mergeCell ref="CQ1:CS1"/>
+    <mergeCell ref="CN2:CP2"/>
+    <mergeCell ref="CQ2:CS2"/>
+    <mergeCell ref="CN3:CP3"/>
+    <mergeCell ref="CQ3:CS3"/>
   </mergeCells>
   <conditionalFormatting sqref="G2">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThanOrEqual">
